--- a/backend/uploads/data.xlsx
+++ b/backend/uploads/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Harshini\Yukta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9FC554FB-FE61-4D43-9D22-4A5C7F708CC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC5CECE1-724C-479E-99BB-D6F71586FE23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E1714DF0-ACF3-41DE-B3A9-4942A806712E}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7F9C8429-1145-4288-B6DC-431A45C0315B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="42">
   <si>
     <t>Name</t>
   </si>
@@ -45,53 +45,128 @@
     <t>Date</t>
   </si>
   <si>
-    <t>Mail</t>
-  </si>
-  <si>
     <t>Template</t>
   </si>
   <si>
-    <t>Vishnu Kumar V</t>
-  </si>
-  <si>
-    <t>Fast &amp; Curious - Web Drift</t>
-  </si>
-  <si>
-    <t>21.02.2026</t>
-  </si>
-  <si>
     <t>Template1</t>
   </si>
   <si>
-    <t>Mohammed Vasim</t>
-  </si>
-  <si>
-    <t>Harish Pranav V</t>
-  </si>
-  <si>
-    <t>Lokesh P D</t>
-  </si>
-  <si>
-    <t>24z158@psgitech.ac.in</t>
-  </si>
-  <si>
-    <t>24z147@psgitech.ac.in</t>
-  </si>
-  <si>
-    <t>24z163@psgitech.ac.in</t>
-  </si>
-  <si>
-    <t>Template2</t>
-  </si>
-  <si>
-    <t>Template3</t>
+    <t>Karthik Kumar</t>
+  </si>
+  <si>
+    <t>A.Dhivyarupa</t>
+  </si>
+  <si>
+    <t>Prompt Battle</t>
+  </si>
+  <si>
+    <t>21.2.2026</t>
+  </si>
+  <si>
+    <t>Kanishka.V</t>
+  </si>
+  <si>
+    <t>Pooja.K</t>
+  </si>
+  <si>
+    <t>Tarunyasree.H</t>
+  </si>
+  <si>
+    <t>Chandraprakash</t>
+  </si>
+  <si>
+    <t>Paveethiran S K</t>
+  </si>
+  <si>
+    <t>Suthibalan B</t>
+  </si>
+  <si>
+    <t>Manobala.N</t>
+  </si>
+  <si>
+    <t>B.Hariharan</t>
+  </si>
+  <si>
+    <t>K Varsha</t>
+  </si>
+  <si>
+    <t>S Priyadharshini</t>
+  </si>
+  <si>
+    <t>A S Vasuki</t>
+  </si>
+  <si>
+    <t>M Kirthiga</t>
+  </si>
+  <si>
+    <t>S Dhanushya</t>
+  </si>
+  <si>
+    <t>S Yogashree</t>
+  </si>
+  <si>
+    <t>Shravanth</t>
+  </si>
+  <si>
+    <t>Sarvesh Chandru</t>
+  </si>
+  <si>
+    <t>M Nisha</t>
+  </si>
+  <si>
+    <t>Amarnath B</t>
+  </si>
+  <si>
+    <t>Sadhana Shree A</t>
+  </si>
+  <si>
+    <t>Adithya M</t>
+  </si>
+  <si>
+    <t>Dhanoosh Bargav D</t>
+  </si>
+  <si>
+    <t>Chokkalingam B</t>
+  </si>
+  <si>
+    <t>Surya</t>
+  </si>
+  <si>
+    <t>Harshini A</t>
+  </si>
+  <si>
+    <t>Harshini R</t>
+  </si>
+  <si>
+    <t>Praveen Balaji K</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vishanthini </t>
+  </si>
+  <si>
+    <t>Sujith D</t>
+  </si>
+  <si>
+    <t>Abishek M</t>
+  </si>
+  <si>
+    <t>Manju Shree P</t>
+  </si>
+  <si>
+    <t>Rifa Fathima F</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Mayur K S</t>
+  </si>
+  <si>
+    <t>Mehanth T</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -100,22 +175,34 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
       <u/>
-      <sz val="11"/>
-      <color theme="10"/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color theme="1"/>
+      <sz val="8"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -138,22 +225,63 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{15384FF3-D5E0-40B7-B6FD-A0BBAFD56823}"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <dxfs count="4">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
+  <tableStyles count="2" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
+    <tableStyle name="PIXEL PARADOX Frame → Function -style" pivot="0" count="2" xr9:uid="{505FEBA1-F351-42E8-B2FF-1A8466121157}">
+      <tableStyleElement type="firstRowStripe" dxfId="3"/>
+      <tableStyleElement type="secondRowStripe" dxfId="2"/>
+    </tableStyle>
+    <tableStyle name="PIXEL PARADOX Frame → Function -style 2" pivot="0" count="2" xr9:uid="{E40BFD2B-4138-4B51-B6DE-CA0C3DAEF6E2}">
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <tableStyleElement type="secondRowStripe" dxfId="0"/>
+    </tableStyle>
+  </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -461,119 +589,1235 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5280530-994E-4A3E-B54D-3E78F3A772BF}">
-  <dimension ref="A1:F5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A0E9782-7895-4ED6-9877-8A82057DBCB6}">
+  <dimension ref="A1:D177"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2"/>
-      <c r="F1" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" s="5" t="s">
+      <c r="B6" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="4"/>
-      <c r="F2" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" s="5" t="s">
+      <c r="B7" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="4"/>
-      <c r="F3" s="3" t="s">
+      <c r="B8" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" s="3" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E4" s="4"/>
-      <c r="F4" s="3" t="s">
+      <c r="B10" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E5" s="4"/>
-      <c r="F5" s="3" t="s">
-        <v>15</v>
-      </c>
+      <c r="B11" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A17" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A18" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A19" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A20" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A21" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A22" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A23" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A24" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A25" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A26" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A27" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A28" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A29" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A30" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A31" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A32" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A33" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A34" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A35" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A36" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A37" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A38" s="1"/>
+      <c r="B38" s="1"/>
+      <c r="C38" s="2"/>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A39" s="1"/>
+      <c r="B39" s="1"/>
+      <c r="C39" s="2"/>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A40" s="1"/>
+      <c r="B40" s="1"/>
+      <c r="C40" s="2"/>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A41" s="1"/>
+      <c r="B41" s="1"/>
+      <c r="C41" s="2"/>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A42" s="1"/>
+      <c r="B42" s="1"/>
+      <c r="C42" s="2"/>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A43" s="1"/>
+      <c r="B43" s="1"/>
+      <c r="C43" s="2"/>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A44" s="1"/>
+      <c r="B44" s="1"/>
+      <c r="C44" s="2"/>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A45" s="1"/>
+      <c r="B45" s="1"/>
+      <c r="C45" s="2"/>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A46" s="1"/>
+      <c r="B46" s="1"/>
+      <c r="C46" s="1"/>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A47" s="1"/>
+      <c r="B47" s="1"/>
+      <c r="C47" s="2"/>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A48" s="1"/>
+      <c r="B48" s="1"/>
+      <c r="C48" s="2"/>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A49" s="1"/>
+      <c r="B49" s="1"/>
+      <c r="C49" s="2"/>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A50" s="1"/>
+      <c r="B50" s="1"/>
+      <c r="C50" s="2"/>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A51" s="1"/>
+      <c r="B51" s="1"/>
+      <c r="C51" s="2"/>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A52" s="1"/>
+      <c r="B52" s="1"/>
+      <c r="C52" s="2"/>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A53" s="1"/>
+      <c r="B53" s="1"/>
+      <c r="C53" s="2"/>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A54" s="1"/>
+      <c r="B54" s="1"/>
+      <c r="C54" s="2"/>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A55" s="1"/>
+      <c r="B55" s="1"/>
+      <c r="C55" s="2"/>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A56" s="1"/>
+      <c r="B56" s="1"/>
+      <c r="C56" s="2"/>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A57" s="1"/>
+      <c r="B57" s="1"/>
+      <c r="C57" s="2"/>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A58" s="1"/>
+      <c r="B58" s="1"/>
+      <c r="C58" s="2"/>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A59" s="1"/>
+      <c r="B59" s="1"/>
+      <c r="C59" s="2"/>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A60" s="1"/>
+      <c r="B60" s="1"/>
+      <c r="C60" s="2"/>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A61" s="1"/>
+      <c r="B61" s="1"/>
+      <c r="C61" s="2"/>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A62" s="1"/>
+      <c r="B62" s="1"/>
+      <c r="C62" s="2"/>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A63" s="1"/>
+      <c r="B63" s="1"/>
+      <c r="C63" s="2"/>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A64" s="1"/>
+      <c r="B64" s="1"/>
+      <c r="C64" s="2"/>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A65" s="1"/>
+      <c r="B65" s="1"/>
+      <c r="C65" s="2"/>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A66" s="1"/>
+      <c r="B66" s="1"/>
+      <c r="C66" s="2"/>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A67" s="1"/>
+      <c r="B67" s="1"/>
+      <c r="C67" s="2"/>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A68" s="1"/>
+      <c r="B68" s="1"/>
+      <c r="C68" s="2"/>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A69" s="1"/>
+      <c r="B69" s="1"/>
+      <c r="C69" s="2"/>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A70" s="1"/>
+      <c r="B70" s="1"/>
+      <c r="C70" s="2"/>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A71" s="1"/>
+      <c r="B71" s="1"/>
+      <c r="C71" s="2"/>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A72" s="1"/>
+      <c r="B72" s="1"/>
+      <c r="C72" s="2"/>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A73" s="1"/>
+      <c r="B73" s="1"/>
+      <c r="C73" s="2"/>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A74" s="1"/>
+      <c r="B74" s="1"/>
+      <c r="C74" s="2"/>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A75" s="1"/>
+      <c r="B75" s="1"/>
+      <c r="C75" s="2"/>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A76" s="1"/>
+      <c r="B76" s="1"/>
+      <c r="C76" s="2"/>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A77" s="1"/>
+      <c r="B77" s="1"/>
+      <c r="C77" s="2"/>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A78" s="1"/>
+      <c r="B78" s="1"/>
+      <c r="C78" s="2"/>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A79" s="1"/>
+      <c r="B79" s="1"/>
+      <c r="C79" s="2"/>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A80" s="1"/>
+      <c r="B80" s="1"/>
+      <c r="C80" s="2"/>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A81" s="1"/>
+      <c r="B81" s="1"/>
+      <c r="C81" s="2"/>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A82" s="1"/>
+      <c r="B82" s="1"/>
+      <c r="C82" s="2"/>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A83" s="1"/>
+      <c r="B83" s="1"/>
+      <c r="C83" s="2"/>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A84" s="1"/>
+      <c r="B84" s="1"/>
+      <c r="C84" s="2"/>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A85" s="1"/>
+      <c r="B85" s="1"/>
+      <c r="C85" s="1"/>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A86" s="1"/>
+      <c r="B86" s="1"/>
+      <c r="C86" s="2"/>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A87" s="1"/>
+      <c r="B87" s="1"/>
+      <c r="C87" s="2"/>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A88" s="1"/>
+      <c r="B88" s="1"/>
+      <c r="C88" s="2"/>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A89" s="1"/>
+      <c r="B89" s="1"/>
+      <c r="C89" s="2"/>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A90" s="1"/>
+      <c r="B90" s="1"/>
+      <c r="C90" s="2"/>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A91" s="1"/>
+      <c r="B91" s="1"/>
+      <c r="C91" s="2"/>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A92" s="1"/>
+      <c r="B92" s="1"/>
+      <c r="C92" s="2"/>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A93" s="1"/>
+      <c r="B93" s="1"/>
+      <c r="C93" s="2"/>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A94" s="1"/>
+      <c r="B94" s="1"/>
+      <c r="C94" s="2"/>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A95" s="1"/>
+      <c r="B95" s="1"/>
+      <c r="C95" s="2"/>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A96" s="1"/>
+      <c r="B96" s="1"/>
+      <c r="C96" s="2"/>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A97" s="1"/>
+      <c r="B97" s="1"/>
+      <c r="C97" s="2"/>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A98" s="1"/>
+      <c r="B98" s="1"/>
+      <c r="C98" s="2"/>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A99" s="1"/>
+      <c r="B99" s="1"/>
+      <c r="C99" s="2"/>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A100" s="1"/>
+      <c r="B100" s="1"/>
+      <c r="C100" s="2"/>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A101" s="1"/>
+      <c r="B101" s="1"/>
+      <c r="C101" s="2"/>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A102" s="1"/>
+      <c r="B102" s="1"/>
+      <c r="C102" s="2"/>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A103" s="1"/>
+      <c r="B103" s="1"/>
+      <c r="C103" s="2"/>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A104" s="1"/>
+      <c r="B104" s="1"/>
+      <c r="C104" s="2"/>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A105" s="1"/>
+      <c r="B105" s="1"/>
+      <c r="C105" s="2"/>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A106" s="1"/>
+      <c r="B106" s="1"/>
+      <c r="C106" s="2"/>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A107" s="1"/>
+      <c r="B107" s="1"/>
+      <c r="C107" s="2"/>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A108" s="1"/>
+      <c r="B108" s="1"/>
+      <c r="C108" s="2"/>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A109" s="1"/>
+      <c r="B109" s="1"/>
+      <c r="C109" s="2"/>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A110" s="1"/>
+      <c r="B110" s="1"/>
+      <c r="C110" s="2"/>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A111" s="1"/>
+      <c r="B111" s="1"/>
+      <c r="C111" s="2"/>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A112" s="1"/>
+      <c r="B112" s="1"/>
+      <c r="C112" s="2"/>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A113" s="1"/>
+      <c r="B113" s="1"/>
+      <c r="C113" s="2"/>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A114" s="1"/>
+      <c r="B114" s="1"/>
+      <c r="C114" s="2"/>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A115" s="1"/>
+      <c r="B115" s="1"/>
+      <c r="C115" s="2"/>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A116" s="1"/>
+      <c r="B116" s="1"/>
+      <c r="C116" s="2"/>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A117" s="1"/>
+      <c r="B117" s="1"/>
+      <c r="C117" s="2"/>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A118" s="1"/>
+      <c r="B118" s="1"/>
+      <c r="C118" s="2"/>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A119" s="1"/>
+      <c r="B119" s="1"/>
+      <c r="C119" s="2"/>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A120" s="1"/>
+      <c r="B120" s="1"/>
+      <c r="C120" s="2"/>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A121" s="1"/>
+      <c r="B121" s="1"/>
+      <c r="C121" s="2"/>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A122" s="1"/>
+      <c r="B122" s="1"/>
+      <c r="C122" s="2"/>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A123" s="1"/>
+      <c r="B123" s="1"/>
+      <c r="C123" s="2"/>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A124" s="1"/>
+      <c r="B124" s="1"/>
+      <c r="C124" s="2"/>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A125" s="1"/>
+      <c r="B125" s="1"/>
+      <c r="C125" s="2"/>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A126" s="1"/>
+      <c r="B126" s="1"/>
+      <c r="C126" s="2"/>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A127" s="1"/>
+      <c r="B127" s="1"/>
+      <c r="C127" s="2"/>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A128" s="1"/>
+      <c r="B128" s="1"/>
+      <c r="C128" s="2"/>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A129" s="1"/>
+      <c r="B129" s="1"/>
+      <c r="C129" s="2"/>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A130" s="1"/>
+      <c r="B130" s="1"/>
+      <c r="C130" s="2"/>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A131" s="1"/>
+      <c r="B131" s="1"/>
+      <c r="C131" s="2"/>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A132" s="1"/>
+      <c r="B132" s="1"/>
+      <c r="C132" s="2"/>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A133" s="1"/>
+      <c r="B133" s="1"/>
+      <c r="C133" s="2"/>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A134" s="1"/>
+      <c r="B134" s="1"/>
+      <c r="C134" s="2"/>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A135" s="1"/>
+      <c r="B135" s="1"/>
+      <c r="C135" s="2"/>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A136" s="1"/>
+      <c r="B136" s="1"/>
+      <c r="C136" s="2"/>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A137" s="1"/>
+      <c r="B137" s="1"/>
+      <c r="C137" s="2"/>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A138" s="1"/>
+      <c r="B138" s="1"/>
+      <c r="C138" s="2"/>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A139" s="1"/>
+      <c r="B139" s="1"/>
+      <c r="C139" s="2"/>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A140" s="1"/>
+      <c r="B140" s="1"/>
+      <c r="C140" s="2"/>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A141" s="1"/>
+      <c r="B141" s="1"/>
+      <c r="C141" s="2"/>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A142" s="1"/>
+      <c r="B142" s="1"/>
+      <c r="C142" s="2"/>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A143" s="1"/>
+      <c r="B143" s="1"/>
+      <c r="C143" s="2"/>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A144" s="1"/>
+      <c r="B144" s="1"/>
+      <c r="C144" s="2"/>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A145" s="1"/>
+      <c r="B145" s="1"/>
+      <c r="C145" s="2"/>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A146" s="1"/>
+      <c r="B146" s="1"/>
+      <c r="C146" s="2"/>
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A147" s="1"/>
+      <c r="B147" s="1"/>
+      <c r="C147" s="2"/>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A148" s="1"/>
+      <c r="B148" s="1"/>
+      <c r="C148" s="2"/>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A149" s="1"/>
+      <c r="B149" s="1"/>
+      <c r="C149" s="2"/>
+    </row>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A150" s="1"/>
+      <c r="B150" s="1"/>
+      <c r="C150" s="2"/>
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A151" s="1"/>
+      <c r="B151" s="1"/>
+      <c r="C151" s="2"/>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A152" s="1"/>
+      <c r="B152" s="1"/>
+      <c r="C152" s="2"/>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A153" s="1"/>
+      <c r="B153" s="1"/>
+      <c r="C153" s="2"/>
+    </row>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A154" s="1"/>
+      <c r="B154" s="1"/>
+      <c r="C154" s="2"/>
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A155" s="1"/>
+      <c r="B155" s="1"/>
+      <c r="C155" s="2"/>
+    </row>
+    <row r="156" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A156" s="1"/>
+      <c r="B156" s="1"/>
+      <c r="C156" s="2"/>
+    </row>
+    <row r="157" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A157" s="1"/>
+      <c r="B157" s="1"/>
+      <c r="C157" s="2"/>
+    </row>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A158" s="1"/>
+      <c r="B158" s="1"/>
+      <c r="C158" s="2"/>
+    </row>
+    <row r="159" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A159" s="1"/>
+      <c r="B159" s="1"/>
+      <c r="C159" s="2"/>
+    </row>
+    <row r="160" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A160" s="1"/>
+      <c r="B160" s="1"/>
+      <c r="C160" s="2"/>
+    </row>
+    <row r="161" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A161" s="1"/>
+      <c r="B161" s="1"/>
+      <c r="C161" s="2"/>
+    </row>
+    <row r="162" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A162" s="1"/>
+      <c r="B162" s="1"/>
+      <c r="C162" s="2"/>
+    </row>
+    <row r="163" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A163" s="1"/>
+      <c r="B163" s="1"/>
+      <c r="C163" s="2"/>
+    </row>
+    <row r="164" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A164" s="1"/>
+      <c r="B164" s="1"/>
+      <c r="C164" s="2"/>
+    </row>
+    <row r="165" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A165" s="1"/>
+      <c r="B165" s="1"/>
+      <c r="C165" s="2"/>
+    </row>
+    <row r="166" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A166" s="1"/>
+      <c r="B166" s="1"/>
+      <c r="C166" s="2"/>
+    </row>
+    <row r="167" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A167" s="1"/>
+      <c r="B167" s="1"/>
+      <c r="C167" s="2"/>
+    </row>
+    <row r="168" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A168" s="1"/>
+      <c r="B168" s="1"/>
+      <c r="C168" s="2"/>
+    </row>
+    <row r="169" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A169" s="1"/>
+      <c r="B169" s="1"/>
+      <c r="C169" s="2"/>
+    </row>
+    <row r="170" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A170" s="1"/>
+      <c r="B170" s="1"/>
+      <c r="C170" s="2"/>
+    </row>
+    <row r="171" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A171" s="1"/>
+      <c r="B171" s="1"/>
+      <c r="C171" s="2"/>
+    </row>
+    <row r="172" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A172" s="1"/>
+      <c r="B172" s="1"/>
+      <c r="C172" s="2"/>
+    </row>
+    <row r="173" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A173" s="1"/>
+      <c r="B173" s="1"/>
+      <c r="C173" s="2"/>
+    </row>
+    <row r="174" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A174" s="1"/>
+      <c r="B174" s="1"/>
+      <c r="C174" s="2"/>
+    </row>
+    <row r="175" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A175" s="1"/>
+      <c r="B175" s="1"/>
+      <c r="C175" s="2"/>
+    </row>
+    <row r="176" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A176" s="1"/>
+      <c r="B176" s="1"/>
+      <c r="C176" s="2"/>
+    </row>
+    <row r="177" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A177" s="1"/>
+      <c r="B177" s="1"/>
+      <c r="C177" s="2"/>
     </row>
   </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="D5:E5"/>
-  </mergeCells>
+  <phoneticPr fontId="5" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C2:C5" xr:uid="{8199EDD4-5666-4898-B36A-24996FB83899}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B2:B177" xr:uid="{AD25D03A-51F6-43EB-89F1-0B554C8B1937}">
       <formula1>"21.02.2026,20/02/2026,21/02/2026,20/02/2027,20/02/2028,20/02/2029,20/02/2030,20.02.2026,21-02-2026,21.2.2026"</formula1>
     </dataValidation>
   </dataValidations>
-  <hyperlinks>
-    <hyperlink ref="D5" r:id="rId1" xr:uid="{8E7C9998-7FBC-4B32-8B02-7FD4058BBC67}"/>
-    <hyperlink ref="D4" r:id="rId2" xr:uid="{822BCCAA-22C1-4AD9-AC9E-624BE40E9DB0}"/>
-    <hyperlink ref="D3" r:id="rId3" xr:uid="{625E75DF-358B-4DD8-93DA-9E56B5A29B03}"/>
-    <hyperlink ref="D2" r:id="rId4" xr:uid="{A7D55CFF-C7F7-4162-9A39-5BACCBA83745}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>